--- a/artfynd/A 32491-2025 artfynd.xlsx
+++ b/artfynd/A 32491-2025 artfynd.xlsx
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126361597</v>
+        <v>126364330</v>
       </c>
       <c r="B5" t="n">
-        <v>57816</v>
+        <v>58084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600419</v>
+        <v>600388</v>
       </c>
       <c r="R5" t="n">
-        <v>6923683</v>
+        <v>6923535</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126364330</v>
+        <v>126361597</v>
       </c>
       <c r="B6" t="n">
-        <v>58084</v>
+        <v>57816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600388</v>
+        <v>600419</v>
       </c>
       <c r="R6" t="n">
-        <v>6923535</v>
+        <v>6923683</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126361902</v>
+        <v>126361818</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>91242</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,39 +1400,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600423</v>
+        <v>600428</v>
       </c>
       <c r="R9" t="n">
-        <v>6923763</v>
+        <v>6923719</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,11 +1460,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126361818</v>
+        <v>126361902</v>
       </c>
       <c r="B10" t="n">
-        <v>91242</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,34 +1497,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600428</v>
+        <v>600423</v>
       </c>
       <c r="R10" t="n">
-        <v>6923719</v>
+        <v>6923763</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,6 +1562,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 32491-2025 artfynd.xlsx
+++ b/artfynd/A 32491-2025 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126361818</v>
+        <v>126361902</v>
       </c>
       <c r="B9" t="n">
-        <v>91242</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,34 +1400,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600428</v>
+        <v>600423</v>
       </c>
       <c r="R9" t="n">
-        <v>6923719</v>
+        <v>6923763</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,6 +1465,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126361902</v>
+        <v>126361818</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>91242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,39 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600423</v>
+        <v>600428</v>
       </c>
       <c r="R10" t="n">
-        <v>6923763</v>
+        <v>6923719</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,11 +1567,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 32491-2025 artfynd.xlsx
+++ b/artfynd/A 32491-2025 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126361902</v>
+        <v>126361818</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>91242</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,39 +1400,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600423</v>
+        <v>600428</v>
       </c>
       <c r="R9" t="n">
-        <v>6923763</v>
+        <v>6923719</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,11 +1460,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126361818</v>
+        <v>126361902</v>
       </c>
       <c r="B10" t="n">
-        <v>91242</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,34 +1497,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600428</v>
+        <v>600423</v>
       </c>
       <c r="R10" t="n">
-        <v>6923719</v>
+        <v>6923763</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,6 +1562,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 32491-2025 artfynd.xlsx
+++ b/artfynd/A 32491-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126362312</v>
       </c>
       <c r="B2" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126363164</v>
       </c>
       <c r="B3" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126361652</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126364330</v>
       </c>
       <c r="B5" t="n">
-        <v>58084</v>
+        <v>58087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>126361597</v>
       </c>
       <c r="B6" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126363951</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>126364021</v>
       </c>
       <c r="B8" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>126361818</v>
       </c>
       <c r="B9" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>126361902</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32491-2025 artfynd.xlsx
+++ b/artfynd/A 32491-2025 artfynd.xlsx
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126364330</v>
+        <v>126361597</v>
       </c>
       <c r="B5" t="n">
-        <v>58087</v>
+        <v>57817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600388</v>
+        <v>600419</v>
       </c>
       <c r="R5" t="n">
-        <v>6923535</v>
+        <v>6923683</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126361597</v>
+        <v>126364330</v>
       </c>
       <c r="B6" t="n">
-        <v>57817</v>
+        <v>58087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600419</v>
+        <v>600388</v>
       </c>
       <c r="R6" t="n">
-        <v>6923683</v>
+        <v>6923535</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 32491-2025 artfynd.xlsx
+++ b/artfynd/A 32491-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>126361652</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126363951</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>126361902</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32491-2025 artfynd.xlsx
+++ b/artfynd/A 32491-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>126361652</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126363951</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>126361902</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32491-2025 artfynd.xlsx
+++ b/artfynd/A 32491-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126362312</v>
+        <v>126361818</v>
       </c>
       <c r="B2" t="n">
-        <v>100450</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600438</v>
+        <v>600428</v>
       </c>
       <c r="R2" t="n">
-        <v>6923759</v>
+        <v>6923719</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,45 +772,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126363164</v>
+        <v>126361652</v>
       </c>
       <c r="B3" t="n">
-        <v>97239</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600532</v>
+        <v>600419</v>
       </c>
       <c r="R3" t="n">
-        <v>6923851</v>
+        <v>6923683</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126361652</v>
+        <v>126361902</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600419</v>
+        <v>600423</v>
       </c>
       <c r="R4" t="n">
-        <v>6923683</v>
+        <v>6923763</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126364330</v>
+        <v>126363951</v>
       </c>
       <c r="B5" t="n">
-        <v>58087</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,27 +997,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1016,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600388</v>
+        <v>600448</v>
       </c>
       <c r="R5" t="n">
-        <v>6923535</v>
+        <v>6923651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126361597</v>
+        <v>126364330</v>
       </c>
       <c r="B6" t="n">
-        <v>57817</v>
+        <v>58388</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600419</v>
+        <v>600388</v>
       </c>
       <c r="R6" t="n">
-        <v>6923683</v>
+        <v>6923535</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,27 +1195,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126363951</v>
+        <v>126364021</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1211,7 +1226,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1220,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600448</v>
+        <v>600453</v>
       </c>
       <c r="R7" t="n">
-        <v>6923651</v>
+        <v>6923666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,38 +1297,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126364021</v>
+        <v>126361597</v>
       </c>
       <c r="B8" t="n">
-        <v>58027</v>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1327,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600453</v>
+        <v>600419</v>
       </c>
       <c r="R8" t="n">
-        <v>6923666</v>
+        <v>6923683</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,32 +1399,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126361818</v>
+        <v>126363164</v>
       </c>
       <c r="B9" t="n">
-        <v>91245</v>
+        <v>97983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600428</v>
+        <v>600532</v>
       </c>
       <c r="R9" t="n">
-        <v>6923719</v>
+        <v>6923851</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1486,50 +1496,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126361902</v>
+        <v>126362312</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>101228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600423</v>
+        <v>600438</v>
       </c>
       <c r="R10" t="n">
-        <v>6923763</v>
+        <v>6923759</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,11 +1567,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 32491-2025 artfynd.xlsx
+++ b/artfynd/A 32491-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126361818</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126361652</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126361902</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126363951</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126364330</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126364021</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126361597</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126363164</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,8 +1635,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126362312</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>